--- a/Tj-Timesheet.xlsx
+++ b/Tj-Timesheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitasgroupaus-my.sharepoint.com/personal/syd27_security_securitas-australia_com_au/Documents/Documents/SAR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Home\tampermonkey_scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="13_ncr:1_{4ADAA32E-E2A7-4B40-8141-54FDF87F451D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AFFC9B0-CC5A-4245-B499-0A8134E701A8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0981305-2731-4BE0-9027-D9A6BD10448C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1032" windowWidth="45144" windowHeight="24168" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -106,16 +106,7 @@
     </r>
   </si>
   <si>
-    <t>SYD27</t>
-  </si>
-  <si>
-    <t>Eastern Creek NSW</t>
-  </si>
-  <si>
     <t>Tajinder Rattan</t>
-  </si>
-  <si>
-    <t>Supervisor</t>
   </si>
   <si>
     <t>Week Commenced:</t>
@@ -141,6 +132,15 @@
       </rPr>
       <t xml:space="preserve">am on Monday </t>
     </r>
+  </si>
+  <si>
+    <t>SYD08</t>
+  </si>
+  <si>
+    <t>Seven Hills, NSW</t>
+  </si>
+  <si>
+    <t>CRS</t>
   </si>
 </sst>
 </file>
@@ -972,23 +972,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T28"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="23.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.75" style="2" customWidth="1"/>
-    <col min="5" max="6" width="12.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="2" customWidth="1"/>
-    <col min="9" max="11" width="12.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="20.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="39.19921875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.69921875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.09765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.69921875" style="2" customWidth="1"/>
+    <col min="5" max="6" width="12.59765625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.59765625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.69921875" style="2" customWidth="1"/>
+    <col min="9" max="11" width="12.59765625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="20.19921875" style="2" customWidth="1"/>
     <col min="13" max="13" width="15.5" style="2" customWidth="1"/>
-    <col min="14" max="14" width="22.625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="8.75" style="2"/>
+    <col min="14" max="14" width="22.59765625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="8.69921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26"/>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -1006,12 +1006,12 @@
       <c r="M1" s="26"/>
       <c r="N1" s="12"/>
     </row>
-    <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -1021,26 +1021,26 @@
       <c r="H2" s="34"/>
       <c r="I2" s="34"/>
       <c r="J2" s="33" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K2" s="40">
         <f>WEEKDAY(D6, 2)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L2" s="27"/>
       <c r="M2" s="27"/>
       <c r="N2" s="4"/>
     </row>
-    <row r="3" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="53">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="E3" s="53"/>
       <c r="F3" s="53"/>
@@ -1048,11 +1048,11 @@
       <c r="H3" s="4"/>
       <c r="I3" s="36"/>
       <c r="J3" s="33" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K3" s="49">
         <f>D6-WEEKDAY(D6, 2)+1</f>
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="L3" s="49"/>
       <c r="M3" s="49"/>
@@ -1062,7 +1062,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
     </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="50"/>
       <c r="C4" s="50"/>
@@ -1083,7 +1083,7 @@
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
     </row>
-    <row r="5" spans="1:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
         <v>1</v>
       </c>
@@ -1126,23 +1126,23 @@
       <c r="N5" s="14"/>
       <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:20" s="25" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" s="25" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" s="41">
         <v>409425023</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D6" s="38">
         <f>D3</f>
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="E6" s="39" t="str">
         <f>TEXT(D6, "ddd")</f>
-        <v>Fri</v>
+        <v>Tue</v>
       </c>
       <c r="F6" s="30">
         <v>0.25</v>
@@ -1160,7 +1160,7 @@
       <c r="M6" s="22"/>
       <c r="N6" s="24"/>
     </row>
-    <row r="7" spans="1:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="21"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -1176,7 +1176,7 @@
       <c r="M7" s="20"/>
       <c r="N7" s="15"/>
     </row>
-    <row r="8" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="1"/>
@@ -1195,7 +1195,7 @@
       <c r="Q8" s="2"/>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="1"/>
@@ -1214,7 +1214,7 @@
       <c r="Q9" s="2"/>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="1"/>
@@ -1233,7 +1233,7 @@
       <c r="Q10" s="2"/>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="1"/>
@@ -1251,7 +1251,7 @@
       <c r="O11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="1"/>
@@ -1269,7 +1269,7 @@
       <c r="O12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="1"/>
@@ -1288,7 +1288,7 @@
       <c r="Q13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="1"/>
@@ -1306,7 +1306,7 @@
       <c r="O14" s="2"/>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="1"/>
@@ -1324,7 +1324,7 @@
       <c r="O15" s="2"/>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="1"/>
@@ -1342,7 +1342,7 @@
       <c r="O16" s="2"/>
       <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
       <c r="C17" s="1"/>
@@ -1360,7 +1360,7 @@
       <c r="O17" s="2"/>
       <c r="Q17" s="2"/>
     </row>
-    <row r="18" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="1"/>
@@ -1378,7 +1378,7 @@
       <c r="O18" s="2"/>
       <c r="Q18" s="2"/>
     </row>
-    <row r="19" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="1"/>
@@ -1396,7 +1396,7 @@
       <c r="O19" s="2"/>
       <c r="Q19" s="2"/>
     </row>
-    <row r="20" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="1"/>
@@ -1414,7 +1414,7 @@
       <c r="O20" s="2"/>
       <c r="Q20" s="2"/>
     </row>
-    <row r="21" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="1"/>
@@ -1432,7 +1432,7 @@
       <c r="O21" s="2"/>
       <c r="Q21" s="2"/>
     </row>
-    <row r="22" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="1"/>
@@ -1450,7 +1450,7 @@
       <c r="O22" s="2"/>
       <c r="Q22" s="2"/>
     </row>
-    <row r="23" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="1"/>
@@ -1468,7 +1468,7 @@
       <c r="O23" s="2"/>
       <c r="Q23" s="2"/>
     </row>
-    <row r="24" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="1"/>
@@ -1486,7 +1486,7 @@
       <c r="O24" s="2"/>
       <c r="Q24" s="2"/>
     </row>
-    <row r="25" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" s="11" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="1"/>
@@ -1504,9 +1504,9 @@
       <c r="O25" s="2"/>
       <c r="Q25" s="2"/>
     </row>
-    <row r="26" spans="1:17" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="51" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B26" s="52"/>
       <c r="C26" s="52"/>
@@ -1522,7 +1522,7 @@
       <c r="M26" s="52"/>
       <c r="N26" s="16"/>
     </row>
-    <row r="27" spans="1:17" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="45" t="s">
         <v>16</v>
       </c>
@@ -1539,14 +1539,14 @@
       <c r="L27" s="46"/>
       <c r="M27" s="46"/>
     </row>
-    <row r="28" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I28" s="37" t="s">
         <v>15</v>
       </c>
       <c r="M28" s="17"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+R1xWAtd4Jyd+EycsWUa/alXSG7wdavKHieEFjs8HgeOStGM1xyvT//No+SWjbR8OI1yZAYinWA8TrnAjy0MgA==" saltValue="hkOlwzWb70fXwPypQyOoGg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Z1HqCNQKUIQM/KsfA8Kexk2SjFhMgRK6Z+2sv3aaPC4jGq3n606/eBEEMmr0G8S7oa3vQE2EPKb7tVtulvI9Vw==" saltValue="7x12Lg+LXLYwsv0PwCjN2g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="A27:M27"/>
@@ -1575,17 +1575,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A427A6D-7028-4FDD-B4B5-3A4CBF7B9107}">
   <dimension ref="B1:M1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.75" customWidth="1"/>
+    <col min="2" max="2" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="43" t="str">
         <f>TEXT($M$1+COLUMN(A1)-1,"ddd dd/mm")</f>
         <v>Mon 13/10</v>
@@ -1626,28 +1626,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D797E06C-5BB0-4520-A8D2-B19226E60E97}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010055704F0FC416CC4AA9ED81046C7B1F6F" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d322c80fcfb73081d1b516cec9719e32">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="797f58d5-0e3c-4990-96bd-2abe7a1db336" xmlns:ns4="15a539e3-a703-4def-a7aa-c1d814a7229e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f2702ea98511b4afa4f9f1c9d844f1b6" ns3:_="" ns4:_="">
     <xsd:import namespace="797f58d5-0e3c-4990-96bd-2abe7a1db336"/>
@@ -1856,25 +1841,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9079810-0566-4006-9CB1-96B48ABA098D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7479DB-D67C-4271-8270-52D208996F93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8FB428-D299-427A-9964-8A5D1D47FC00}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1894,6 +1876,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7479DB-D67C-4271-8270-52D208996F93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9079810-0566-4006-9CB1-96B48ABA098D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{f24354d6-c0e9-4261-9371-01f058dc89e3}" enabled="1" method="Standard" siteId="{fb0af7d1-8a83-48bc-8d2d-cd92034c79d4}" contentBits="2" removed="0"/>
